--- a/Jhaver_Directors_Master.xlsx
+++ b/Jhaver_Directors_Master.xlsx
@@ -7,8 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Jhaver Directors" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Notes &amp; Sources" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Directors" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Company Master" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Probe42 Endpoint Map" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Notes &amp; Sources" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -76,22 +78,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -458,20 +451,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K44"/>
+  <dimension ref="A1:L44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
-    <col width="32" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="32" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -492,40 +486,45 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>UCIC</t>
+          <t>UCIC (CIN)</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>A/c Holder</t>
+          <t>Company PAN (Probe42 GSTIN-derived)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>A/c Holder (Director)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Realtime Designation</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>DIN</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>PODS PAN</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>DoI-DoB</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Mobile No</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Email ID</t>
         </is>
@@ -535,1514 +534,1717 @@
       <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>Jhaver Group</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Jhaver Group</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Tagros Chemicals India Pvt Ltd</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>U24294TN1992PTC024115</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>AAACT2952K</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>Parikshith Jhaver</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Whole-Time Director</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>00341448</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr"/>
-      <c r="I2" s="3" t="inlineStr"/>
-      <c r="J2" s="3" t="inlineStr"/>
-      <c r="K2" s="3" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>Jhaver Group</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Jhaver Group</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Tagros Chemicals India Pvt Ltd</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>U24294TN1992PTC024115</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>AAACT2952K</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Devkishan Jhaver</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Director</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>00415238</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr"/>
-      <c r="I3" s="3" t="inlineStr"/>
-      <c r="J3" s="3" t="inlineStr"/>
-      <c r="K3" s="3" t="inlineStr"/>
+      <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Jhaver Group</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Jhaver Group</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Tagros Chemicals India Pvt Ltd</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>U24294TN1992PTC024115</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>AAACT2952K</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Abhimanyu Jhaver</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Director</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr"/>
-      <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="3" t="inlineStr"/>
-      <c r="J4" s="3" t="inlineStr"/>
-      <c r="K4" s="3" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Jhaver Group</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Jhaver Group</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Tagros Chemicals India Pvt Ltd</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>U24294TN1992PTC024115</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>AAACT2952K</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Sunish Kuttappan Nair</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Independent Director</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr"/>
-      <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="3" t="inlineStr"/>
-      <c r="J5" s="3" t="inlineStr"/>
-      <c r="K5" s="3" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Jhaver Group</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Jhaver Group</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Tagros Chemicals India Pvt Ltd</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>U24294TN1992PTC024115</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>AAACT2952K</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Venkatachalam Kailasam</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Independent Director</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr"/>
-      <c r="H6" s="3" t="inlineStr"/>
-      <c r="I6" s="3" t="inlineStr"/>
-      <c r="J6" s="3" t="inlineStr"/>
-      <c r="K6" s="3" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Jhaver Group</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Jhaver Group</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>Tagros Chemicals India Pvt Ltd</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>U24294TN1992PTC024115</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>AAACT2952K</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Kuppuswamy Rajagopal</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>Independent Director</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr"/>
-      <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="inlineStr"/>
-      <c r="J7" s="3" t="inlineStr"/>
-      <c r="K7" s="3" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Jhaver Group</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Jhaver Group</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>Tagros Chemicals India Pvt Ltd</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>U24294TN1992PTC024115</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>AAACT2952K</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Jobi Eapen</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>President - Sales</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr"/>
-      <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="3" t="inlineStr"/>
-      <c r="J8" s="3" t="inlineStr"/>
-      <c r="K8" s="3" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Jhaver Group</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Jhaver Group</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>Tagros Chemicals India Pvt Ltd</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>U24294TN1992PTC024115</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>AAACT2952K</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Abhijit Bose</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>CMO</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr"/>
-      <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="3" t="inlineStr"/>
-      <c r="J9" s="3" t="inlineStr"/>
-      <c r="K9" s="3" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Jhaver Group</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Jhaver Group</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>Tagros Chemicals India Pvt Ltd</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>U24294TN1992PTC024115</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>AAACT2952K</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Thamizhanban Shanmugam</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>Head - Regulatory Affairs</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr"/>
-      <c r="H10" s="3" t="inlineStr"/>
-      <c r="I10" s="3" t="inlineStr"/>
-      <c r="J10" s="3" t="inlineStr"/>
-      <c r="K10" s="3" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>Jhaver Group</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Jhaver Group</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>Tropical Agrosystem India Pvt Ltd</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>U74110TN1969PTC005774</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>AAACT4250E</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>V.K. Jhaver</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>Chairman</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr"/>
-      <c r="H11" s="3" t="inlineStr"/>
-      <c r="I11" s="3" t="inlineStr"/>
-      <c r="J11" s="3" t="inlineStr"/>
-      <c r="K11" s="3" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Jhaver Group</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Jhaver Group</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>Tropical Agrosystem India Pvt Ltd</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>U74110TN1969PTC005774</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>AAACT4250E</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Yogesh Dwivedi</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>Director</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr"/>
-      <c r="H12" s="3" t="inlineStr"/>
-      <c r="I12" s="3" t="inlineStr"/>
-      <c r="J12" s="3" t="inlineStr"/>
-      <c r="K12" s="3" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Jhaver Group</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Jhaver Group</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>Tropical Agrosystem India Pvt Ltd</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>U74110TN1969PTC005774</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>AAACT4250E</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>Dinesh Kumar</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>Director</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr"/>
-      <c r="H13" s="3" t="inlineStr"/>
-      <c r="I13" s="3" t="inlineStr"/>
-      <c r="J13" s="3" t="inlineStr"/>
-      <c r="K13" s="3" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Jhaver Group</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Jhaver Group</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>Tropical Agrosystem India Pvt Ltd</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>U74110TN1969PTC005774</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>AAACT4250E</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Jayaprakash Sadeeshkumar</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>Director</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr"/>
-      <c r="H14" s="3" t="inlineStr"/>
-      <c r="I14" s="3" t="inlineStr"/>
-      <c r="J14" s="3" t="inlineStr"/>
-      <c r="K14" s="3" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>Jhaver Group</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Jhaver Group</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>Tropical Agrosystem India Pvt Ltd</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>U74110TN1969PTC005774</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>AAACT4250E</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>Thiruvengadam Gurumoorthy</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>Director</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr"/>
-      <c r="H15" s="3" t="inlineStr"/>
-      <c r="I15" s="3" t="inlineStr"/>
-      <c r="J15" s="3" t="inlineStr"/>
-      <c r="K15" s="3" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Jhaver Group</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Jhaver Group</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>Prodapt Solutions Pvt Ltd</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>U30007TN1999PTC041798</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>AAACZ0985G</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Vedant Jhaver</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>Founder / Chairman</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr"/>
-      <c r="H16" s="3" t="inlineStr"/>
-      <c r="I16" s="3" t="inlineStr"/>
-      <c r="J16" s="3" t="inlineStr"/>
-      <c r="K16" s="3" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>Jhaver Group</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Jhaver Group</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>Prodapt Solutions Pvt Ltd</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>U30007TN1999PTC041798</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>AAACZ0985G</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Manish Vyas</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>CEO</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr"/>
-      <c r="H17" s="3" t="inlineStr"/>
-      <c r="I17" s="3" t="inlineStr"/>
-      <c r="J17" s="3" t="inlineStr"/>
-      <c r="K17" s="3" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>Jhaver Group</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Jhaver Group</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>Prodapt Solutions Pvt Ltd</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>U30007TN1999PTC041798</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>AAACZ0985G</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Raju Venkataraman</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>Director</t>
         </is>
       </c>
-      <c r="G18" s="3" t="inlineStr"/>
-      <c r="H18" s="3" t="inlineStr"/>
-      <c r="I18" s="3" t="inlineStr"/>
-      <c r="J18" s="3" t="inlineStr"/>
-      <c r="K18" s="3" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>Jhaver Group</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Jhaver Group</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>Prodapt Solutions Pvt Ltd</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>U30007TN1999PTC041798</t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>AAACZ0985G</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>Antony Jacob</t>
         </is>
       </c>
-      <c r="F19" s="3" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>Director</t>
         </is>
       </c>
-      <c r="G19" s="3" t="inlineStr"/>
-      <c r="H19" s="3" t="inlineStr"/>
-      <c r="I19" s="3" t="inlineStr"/>
-      <c r="J19" s="3" t="inlineStr"/>
-      <c r="K19" s="3" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr"/>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>Jhaver Group</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Jhaver Group</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>Prodapt Solutions Pvt Ltd</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>U30007TN1999PTC041798</t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>AAACZ0985G</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Udai Dhawan</t>
         </is>
       </c>
-      <c r="F20" s="3" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>Director</t>
         </is>
       </c>
-      <c r="G20" s="3" t="inlineStr"/>
-      <c r="H20" s="3" t="inlineStr"/>
-      <c r="I20" s="3" t="inlineStr"/>
-      <c r="J20" s="3" t="inlineStr"/>
-      <c r="K20" s="3" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr"/>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>Jhaver Group</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Jhaver Group</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>Prodapt Solutions Pvt Ltd</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>U30007TN1999PTC041798</t>
         </is>
       </c>
-      <c r="E21" s="3" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>AAACZ0985G</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>Vishnu Vardhan</t>
         </is>
       </c>
-      <c r="F21" s="3" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>Director</t>
         </is>
       </c>
-      <c r="G21" s="3" t="inlineStr"/>
-      <c r="H21" s="3" t="inlineStr"/>
-      <c r="I21" s="3" t="inlineStr"/>
-      <c r="J21" s="3" t="inlineStr"/>
-      <c r="K21" s="3" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr"/>
+      <c r="I21" s="2" t="inlineStr"/>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Jhaver Group</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Jhaver Group</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>Prodapt Solutions Pvt Ltd</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>U30007TN1999PTC041798</t>
         </is>
       </c>
-      <c r="E22" s="3" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>AAACZ0985G</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Jai Kishan Jhaver</t>
         </is>
       </c>
-      <c r="F22" s="3" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>Director</t>
         </is>
       </c>
-      <c r="G22" s="3" t="inlineStr"/>
-      <c r="H22" s="3" t="inlineStr"/>
-      <c r="I22" s="3" t="inlineStr"/>
-      <c r="J22" s="3" t="inlineStr"/>
-      <c r="K22" s="3" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr"/>
+      <c r="I22" s="2" t="inlineStr"/>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>Jhaver Group</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Jhaver Group</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>Tablets (India) Ltd</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>U24231TN1938PLC002883</t>
         </is>
       </c>
-      <c r="E23" s="3" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>AAACT7987L</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>Bharat Jhaver</t>
         </is>
       </c>
-      <c r="F23" s="3" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="G23" s="3" t="inlineStr"/>
-      <c r="H23" s="3" t="inlineStr"/>
-      <c r="I23" s="3" t="inlineStr"/>
-      <c r="J23" s="3" t="inlineStr"/>
-      <c r="K23" s="3" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr"/>
+      <c r="I23" s="2" t="inlineStr"/>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Jhaver Group</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Jhaver Group</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>Tablets (India) Ltd</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>U24231TN1938PLC002883</t>
         </is>
       </c>
-      <c r="E24" s="3" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>AAACT7987L</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Kishor Lal Daga</t>
         </is>
       </c>
-      <c r="F24" s="3" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>Director</t>
         </is>
       </c>
-      <c r="G24" s="3" t="inlineStr"/>
-      <c r="H24" s="3" t="inlineStr"/>
-      <c r="I24" s="3" t="inlineStr"/>
-      <c r="J24" s="3" t="inlineStr"/>
-      <c r="K24" s="3" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr"/>
+      <c r="I24" s="2" t="inlineStr"/>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>Jhaver Group</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Jhaver Group</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>Tablets (India) Ltd</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>U24231TN1938PLC002883</t>
         </is>
       </c>
-      <c r="E25" s="3" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>AAACT7987L</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>Vishwanatha Rao Kambale Vasudev</t>
         </is>
       </c>
-      <c r="F25" s="3" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>Director</t>
         </is>
       </c>
-      <c r="G25" s="3" t="inlineStr"/>
-      <c r="H25" s="3" t="inlineStr"/>
-      <c r="I25" s="3" t="inlineStr"/>
-      <c r="J25" s="3" t="inlineStr"/>
-      <c r="K25" s="3" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr"/>
+      <c r="I25" s="2" t="inlineStr"/>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>Jhaver Group</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Jhaver Group</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>Tablets (India) Ltd</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>U24231TN1938PLC002883</t>
         </is>
       </c>
-      <c r="E26" s="3" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>AAACT7987L</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Murali Madhavan</t>
         </is>
       </c>
-      <c r="F26" s="3" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>Director</t>
         </is>
       </c>
-      <c r="G26" s="3" t="inlineStr"/>
-      <c r="H26" s="3" t="inlineStr"/>
-      <c r="I26" s="3" t="inlineStr"/>
-      <c r="J26" s="3" t="inlineStr"/>
-      <c r="K26" s="3" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr"/>
+      <c r="I26" s="2" t="inlineStr"/>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>Jhaver Group</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Jhaver Group</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>Tablets (India) Ltd</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>U24231TN1938PLC002883</t>
         </is>
       </c>
-      <c r="E27" s="3" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>AAACT7987L</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Parameshwaran M.B.</t>
         </is>
       </c>
-      <c r="F27" s="3" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>Director</t>
         </is>
       </c>
-      <c r="G27" s="3" t="inlineStr"/>
-      <c r="H27" s="3" t="inlineStr"/>
-      <c r="I27" s="3" t="inlineStr"/>
-      <c r="J27" s="3" t="inlineStr"/>
-      <c r="K27" s="3" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr"/>
+      <c r="I27" s="2" t="inlineStr"/>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>Jhaver Group</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Jhaver Group</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>Tablets (India) Ltd</t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>U24231TN1938PLC002883</t>
         </is>
       </c>
-      <c r="E28" s="3" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>AAACT7987L</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Venkatasubramaniam Visweswaran</t>
         </is>
       </c>
-      <c r="F28" s="3" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>Director</t>
         </is>
       </c>
-      <c r="G28" s="3" t="inlineStr"/>
-      <c r="H28" s="3" t="inlineStr"/>
-      <c r="I28" s="3" t="inlineStr"/>
-      <c r="J28" s="3" t="inlineStr"/>
-      <c r="K28" s="3" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr"/>
+      <c r="I28" s="2" t="inlineStr"/>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>Jhaver Group</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Jhaver Group</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>Tablets (India) Ltd</t>
         </is>
       </c>
-      <c r="D29" s="3" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>U24231TN1938PLC002883</t>
         </is>
       </c>
-      <c r="E29" s="3" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>AAACT7987L</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>Ravi Muthuvalathan</t>
         </is>
       </c>
-      <c r="F29" s="3" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>Director</t>
         </is>
       </c>
-      <c r="G29" s="3" t="inlineStr"/>
-      <c r="H29" s="3" t="inlineStr"/>
-      <c r="I29" s="3" t="inlineStr"/>
-      <c r="J29" s="3" t="inlineStr"/>
-      <c r="K29" s="3" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr"/>
+      <c r="I29" s="2" t="inlineStr"/>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>Jhaver Group</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Jhaver Group</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>Tablets (India) Ltd</t>
         </is>
       </c>
-      <c r="D30" s="3" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>U24231TN1938PLC002883</t>
         </is>
       </c>
-      <c r="E30" s="3" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>AAACT7987L</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Shakuntala Daga</t>
         </is>
       </c>
-      <c r="F30" s="3" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>Director</t>
         </is>
       </c>
-      <c r="G30" s="3" t="inlineStr"/>
-      <c r="H30" s="3" t="inlineStr"/>
-      <c r="I30" s="3" t="inlineStr"/>
-      <c r="J30" s="3" t="inlineStr"/>
-      <c r="K30" s="3" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr"/>
+      <c r="I30" s="2" t="inlineStr"/>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>Jhaver Group</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Jhaver Group</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>Tablets (India) Ltd</t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>U24231TN1938PLC002883</t>
         </is>
       </c>
-      <c r="E31" s="3" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>AAACT7987L</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>Ranganathan S.R.</t>
         </is>
       </c>
-      <c r="F31" s="3" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t>Director</t>
         </is>
       </c>
-      <c r="G31" s="3" t="inlineStr"/>
-      <c r="H31" s="3" t="inlineStr"/>
-      <c r="I31" s="3" t="inlineStr"/>
-      <c r="J31" s="3" t="inlineStr"/>
-      <c r="K31" s="3" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr"/>
+      <c r="I31" s="2" t="inlineStr"/>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
         <v>31</v>
       </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>Jhaver Group</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Jhaver Group</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>TIL Healthcare Pvt Ltd</t>
         </is>
       </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>TBC (private CIN)</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>U24231TN1991PTC020206</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>AABCT0985H</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Kapil Jhaver</t>
         </is>
       </c>
-      <c r="F32" s="3" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>Managing Director</t>
         </is>
       </c>
-      <c r="G32" s="3" t="inlineStr"/>
-      <c r="H32" s="3" t="inlineStr"/>
-      <c r="I32" s="3" t="inlineStr"/>
-      <c r="J32" s="3" t="inlineStr"/>
-      <c r="K32" s="3" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr"/>
+      <c r="I32" s="2" t="inlineStr"/>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>Jhaver Group</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Jhaver Group</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>TIL Healthcare Pvt Ltd</t>
         </is>
       </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>TBC (private CIN)</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>U24231TN1991PTC020206</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>AABCT0985H</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Rangarajan Vijayaragavan</t>
         </is>
       </c>
-      <c r="F33" s="3" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>Director</t>
         </is>
       </c>
-      <c r="G33" s="3" t="inlineStr"/>
-      <c r="H33" s="3" t="inlineStr"/>
-      <c r="I33" s="3" t="inlineStr"/>
-      <c r="J33" s="3" t="inlineStr"/>
-      <c r="K33" s="3" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr"/>
+      <c r="I33" s="2" t="inlineStr"/>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>Jhaver Group</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Jhaver Group</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>JU Agri Sciences Pvt Ltd</t>
         </is>
       </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>TBC</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="inlineStr">
-        <is>
-          <t>Vedant Jhaver</t>
-        </is>
-      </c>
-      <c r="F34" s="3" t="inlineStr">
-        <is>
-          <t>Director</t>
-        </is>
-      </c>
-      <c r="G34" s="3" t="inlineStr"/>
-      <c r="H34" s="3" t="inlineStr"/>
-      <c r="I34" s="3" t="inlineStr"/>
-      <c r="J34" s="3" t="inlineStr"/>
-      <c r="K34" s="3" t="inlineStr"/>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>U74899DL1986PTC024176</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>AAACJ0096L</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Mahipal Singh Rathi</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>Director (CSR Committee)</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr"/>
+      <c r="I34" s="2" t="inlineStr"/>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>Jhaver Group</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Jhaver Group</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>JU Agri Sciences Pvt Ltd</t>
         </is>
       </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>TBC</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="inlineStr">
-        <is>
-          <t>Mahipal Singh Rathi</t>
-        </is>
-      </c>
-      <c r="F35" s="3" t="inlineStr">
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>U74899DL1986PTC024176</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>AAACJ0096L</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>Bijendra Kumar</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
         <is>
           <t>Director (CSR Committee)</t>
         </is>
       </c>
-      <c r="G35" s="3" t="inlineStr"/>
-      <c r="H35" s="3" t="inlineStr"/>
-      <c r="I35" s="3" t="inlineStr"/>
-      <c r="J35" s="3" t="inlineStr"/>
-      <c r="K35" s="3" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr"/>
+      <c r="I35" s="2" t="inlineStr"/>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>Jhaver Group</t>
-        </is>
-      </c>
-      <c r="C36" s="3" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Jhaver Group</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>JU Agri Sciences Pvt Ltd</t>
         </is>
       </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t>TBC</t>
-        </is>
-      </c>
-      <c r="E36" s="3" t="inlineStr">
-        <is>
-          <t>Bijendra Kumar</t>
-        </is>
-      </c>
-      <c r="F36" s="3" t="inlineStr">
-        <is>
-          <t>Director (CSR Committee)</t>
-        </is>
-      </c>
-      <c r="G36" s="3" t="inlineStr"/>
-      <c r="H36" s="3" t="inlineStr"/>
-      <c r="I36" s="3" t="inlineStr"/>
-      <c r="J36" s="3" t="inlineStr"/>
-      <c r="K36" s="3" t="inlineStr"/>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>U74899DL1986PTC024176</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>AAACJ0096L</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Vedant Jhaver</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr"/>
+      <c r="I36" s="2" t="inlineStr"/>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
         <v>36</v>
       </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>Jhaver Group</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Jhaver Group</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
         <is>
           <t>JU Agri Sciences Pvt Ltd</t>
         </is>
       </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>TBC</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="inlineStr">
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>U74899DL1986PTC024176</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>AAACJ0096L</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Ramesh Chand Sharma</t>
         </is>
       </c>
-      <c r="F37" s="3" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr">
         <is>
           <t>Director</t>
         </is>
       </c>
-      <c r="G37" s="3" t="inlineStr"/>
-      <c r="H37" s="3" t="inlineStr"/>
-      <c r="I37" s="3" t="inlineStr"/>
-      <c r="J37" s="3" t="inlineStr"/>
-      <c r="K37" s="3" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr"/>
+      <c r="I37" s="2" t="inlineStr"/>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
         <v>37</v>
       </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>Jhaver Group</t>
-        </is>
-      </c>
-      <c r="C38" s="3" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Jhaver Group</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>JU Agri Sciences Pvt Ltd</t>
         </is>
       </c>
-      <c r="D38" s="3" t="inlineStr">
-        <is>
-          <t>TBC</t>
-        </is>
-      </c>
-      <c r="E38" s="3" t="inlineStr">
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>U74899DL1986PTC024176</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>AAACJ0096L</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Shivaji Singh</t>
         </is>
       </c>
-      <c r="F38" s="3" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>Head - Human Resources (CSR Process Owner)</t>
         </is>
       </c>
-      <c r="G38" s="3" t="inlineStr"/>
-      <c r="H38" s="3" t="inlineStr"/>
-      <c r="I38" s="3" t="inlineStr"/>
-      <c r="J38" s="3" t="inlineStr"/>
-      <c r="K38" s="3" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr"/>
+      <c r="I38" s="2" t="inlineStr"/>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
         <v>38</v>
       </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>Jhaver Group</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Jhaver Group</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
         <is>
           <t>Zip Industries Pvt Ltd</t>
         </is>
       </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>TBC</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="inlineStr">
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>U33111TN1956PTC003366</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>AAACZ0949E</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Jai Kishan Jhaver</t>
         </is>
       </c>
-      <c r="F39" s="3" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr">
         <is>
           <t>Director</t>
         </is>
       </c>
-      <c r="G39" s="3" t="inlineStr"/>
-      <c r="H39" s="3" t="inlineStr"/>
-      <c r="I39" s="3" t="inlineStr"/>
-      <c r="J39" s="3" t="inlineStr"/>
-      <c r="K39" s="3" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr"/>
+      <c r="I39" s="2" t="inlineStr"/>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
         <v>39</v>
       </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>Jhaver Group</t>
-        </is>
-      </c>
-      <c r="C40" s="3" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Jhaver Group</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>Zip Industries Pvt Ltd</t>
         </is>
       </c>
-      <c r="D40" s="3" t="inlineStr">
-        <is>
-          <t>TBC</t>
-        </is>
-      </c>
-      <c r="E40" s="3" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>U33111TN1956PTC003366</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>AAACZ0949E</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Gollapudi Vishnu Vardhan</t>
         </is>
       </c>
-      <c r="F40" s="3" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr">
         <is>
           <t>Director</t>
         </is>
       </c>
-      <c r="G40" s="3" t="inlineStr"/>
-      <c r="H40" s="3" t="inlineStr"/>
-      <c r="I40" s="3" t="inlineStr"/>
-      <c r="J40" s="3" t="inlineStr"/>
-      <c r="K40" s="3" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr"/>
+      <c r="I40" s="2" t="inlineStr"/>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>Jhaver Group</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Jhaver Group</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
         <is>
           <t>Zip Industries Pvt Ltd</t>
         </is>
       </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t>TBC</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="inlineStr">
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>U33111TN1956PTC003366</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>AAACZ0949E</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>Subramaniam Raman</t>
         </is>
       </c>
-      <c r="F41" s="3" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr">
         <is>
           <t>Director</t>
         </is>
       </c>
-      <c r="G41" s="3" t="inlineStr"/>
-      <c r="H41" s="3" t="inlineStr"/>
-      <c r="I41" s="3" t="inlineStr"/>
-      <c r="J41" s="3" t="inlineStr"/>
-      <c r="K41" s="3" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr"/>
+      <c r="I41" s="2" t="inlineStr"/>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
         <v>41</v>
       </c>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>Jhaver Group</t>
-        </is>
-      </c>
-      <c r="C42" s="3" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Jhaver Group</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>Arqivo (Tagros B2C subsidiary)</t>
         </is>
       </c>
-      <c r="D42" s="3" t="inlineStr">
-        <is>
-          <t>Subsidiary of U24294TN1992PTC024115</t>
-        </is>
-      </c>
-      <c r="E42" s="3" t="inlineStr">
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Subsidiary of Tagros (CIN TBC)</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr"/>
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>(Same board as Tagros at incorporation)</t>
         </is>
       </c>
-      <c r="F42" s="3" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t>TBC</t>
         </is>
       </c>
-      <c r="G42" s="3" t="inlineStr"/>
-      <c r="H42" s="3" t="inlineStr"/>
-      <c r="I42" s="3" t="inlineStr"/>
-      <c r="J42" s="3" t="inlineStr"/>
-      <c r="K42" s="3" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr"/>
+      <c r="I42" s="2" t="inlineStr"/>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
         <v>42</v>
       </c>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>Jhaver Group</t>
-        </is>
-      </c>
-      <c r="C43" s="3" t="inlineStr">
-        <is>
-          <t>Prodapt Infrastructure Holdings (Prologis JV India)</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t>TBC</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Jhaver Group</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Prodapt Infrastructure / Prologis JV</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>TBC (JV vehicle)</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr"/>
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>Vedant Jhaver</t>
         </is>
       </c>
-      <c r="F43" s="3" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr">
         <is>
           <t>Chairman, Prologis India</t>
         </is>
       </c>
-      <c r="G43" s="3" t="inlineStr"/>
-      <c r="H43" s="3" t="inlineStr"/>
-      <c r="I43" s="3" t="inlineStr"/>
-      <c r="J43" s="3" t="inlineStr"/>
-      <c r="K43" s="3" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr"/>
+      <c r="I43" s="2" t="inlineStr"/>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
         <v>43</v>
       </c>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>Jhaver Group</t>
-        </is>
-      </c>
-      <c r="C44" s="3" t="inlineStr">
-        <is>
-          <t>Prodapt Infrastructure Holdings (Prologis JV India)</t>
-        </is>
-      </c>
-      <c r="D44" s="3" t="inlineStr">
-        <is>
-          <t>TBC</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Jhaver Group</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Prodapt Infrastructure / Prologis JV</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>TBC (JV vehicle)</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr"/>
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Vineet Sekhsaria</t>
         </is>
       </c>
-      <c r="F44" s="3" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>Head - India, Prologis</t>
         </is>
       </c>
-      <c r="G44" s="3" t="inlineStr"/>
-      <c r="H44" s="3" t="inlineStr"/>
-      <c r="I44" s="3" t="inlineStr"/>
-      <c r="J44" s="3" t="inlineStr"/>
-      <c r="K44" s="3" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr"/>
+      <c r="I44" s="2" t="inlineStr"/>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2055,126 +2257,1154 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:R10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="110" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="38" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="60" customWidth="1" min="9" max="9"/>
+    <col width="35" customWidth="1" min="10" max="10"/>
+    <col width="60" customWidth="1" min="11" max="11"/>
+    <col width="26" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="70" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>S.No.</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Promoter/Group</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>CIN</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Company PAN</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Legal Name (GST register)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Active GSTINs</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>States Covered (count)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>States Covered</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>EPFO Estd Name</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>EPFO Address</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>EPFO Payment Timeliness</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Monthly Employees (EPFO)</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Open Charges (count)</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Open Charges (Rs Cr)</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Latest Rating Agency</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Latest Rating Date</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Top Instruments (Rating)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Jhaver Group</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Tagros Chemicals India Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>U24294TN1992PTC024115</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>AAACT2952K</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>TAGROS CHEMICALS INDIA PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Andhra Pradesh, Gujarat, Karnataka, Maharashtra, Punjab, Tamil Nadu, Uttar Pradesh</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>TAGROS CHEMICALS INDIA PVT. LTD</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>72,MARSHALLS ROAD,IV FLOOR, EGMORE,CHENNAI,TAMIL NADU,600008,India</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>Payment After Due Date in last 12 Months.</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>92</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>1388.4</v>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>CRISIL</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>Bank Guarantee A1+ (4.0 Cr); Cash Credit AA (3.0 Cr); Export Packing Credit AA (307.0 Cr); Export Packing Credit AA (287.5 Cr); Export Packing Credit AA (200.0 Cr)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Jhaver Group</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Tropical Agrosystem India Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>U74110TN1969PTC005774</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>AAACT4250E</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>TROPICAL AGRO SYSTEM (INDIA) PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Andhra Pradesh, Assam, Bihar, Chhattisgarh, Delhi, Gujarat, Haryana, Himachal Pradesh, Jammu and Kashmir, Jharkhand, Karnataka, Kerala, Madhya Pradesh, Maharashtra, Odisha, Puducherry, Punjab, Rajasthan, Tamil Nadu, Telangana, Uttar Pradesh, Uttarakhand, West Bengal</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>TROPICAL AGRO SYSTEM INDIA PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>NEW NO.82, OLD NO.195 ST. MARYS ROAD,  ALWARPET,,CHENNAI,TAMIL NADU,600018,India</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>Paid on Time</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>841</v>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>530.21</v>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>CRISIL</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>2025-04-28</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t>Cash Credit A (50.0 Cr); Cash Credit A (50.0 Cr); Cash Credit A (175.0 Cr); Cash Credit A (125.0 Cr); Cash Credit A (125.0 Cr)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Jhaver Group</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Prodapt Solutions Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>U30007TN1999PTC041798</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>AAACZ0985G</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>PRODAPT SOLUTIONS PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Karnataka, Maharashtra, Tamil Nadu, Telangana</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>PRODAPT SOLUTIONS (P) LTD.</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>NO. 25A AND B, SOUTH PHASE, SIDCO INDUSTRIAL ESTATE, GUINDY,,CHENNAI,TAMIL NADU,600032,India</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Payment After Due Date in last 12 Months.</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>2624</v>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>115.25</v>
+      </c>
+      <c r="P4" s="2" t="inlineStr"/>
+      <c r="Q4" s="2" t="inlineStr"/>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>This corporate or any of its financial instruments do not have a credit rating on or after 2015 as per our records.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Jhaver Group</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Tablets (India) Ltd</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>U24231TN1938PLC002883</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>AAACT7987L</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>TABLETS (INDIA) LIMITED</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Andhra Pradesh, Bihar, Delhi, Himachal Pradesh, Jharkhand, Karnataka, Kerala, Madhya Pradesh, Maharashtra, Odisha, Puducherry, Punjab, Rajasthan, Tamil Nadu, Telangana, Uttar Pradesh, Uttarakhand, West Bengal</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>TABLETS (INDIA) LIMITED</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>NO 72, MARSHALLS ROAD, R.A. BUILDING, 4TH FLOOR,  EGMORE,CHENNAI,TAMIL NADU,600008,India</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>Paid on Time</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>1237</v>
+      </c>
+      <c r="N5" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="O5" s="2" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>ICRA</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>Cash Credit (Fund Based) A (62.5 Cr); Short Term Non Fund Based A1 (7.5 Cr); Unallocated Facility (Lon A (5.3 Cr)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Jhaver Group</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>TIL Healthcare Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>U24231TN1991PTC020206</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>AABCT0985H</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>TIL HEALTHCARE PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Andhra Pradesh, Delhi, Gujarat, Maharashtra, Odisha, Puducherry, Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>TIL HEALTHCARE PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>TAGROS HOUSE,3RD FLOOR, NEW NO.4,  CLUB HOUSE ROAD, ANNA SALAI,,CHENNAI,TAMIL NADU,600002,India</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>Payment After Due Date in last 12 Months.</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>148</v>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>506.07</v>
+      </c>
+      <c r="P6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="inlineStr"/>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>This corporate or any of its financial instruments do not have a credit rating on or after 2015 as per our records.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Jhaver Group</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>JU Agri Sciences Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>U74899DL1986PTC024176</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>AAACJ0096L</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>JU AGRI SCIENCES PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Andhra Pradesh, Assam, Bihar, Chhattisgarh, Delhi, Gujarat, Haryana, Jammu and Kashmir, Jharkhand, Karnataka, Kerala, Madhya Pradesh, Maharashtra, Odisha, Punjab, Rajasthan, Tamil Nadu, Telangana, Uttar Pradesh, Uttarakhand, West Bengal</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>J U AGRI SCIENCES PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>906, VISHWADEEP TOWER DISTRIC CENTRE, JANAK PURI,NEW DELHI,DELHI,110058,India</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>Paid on Time</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>488</v>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>210</v>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>CARE</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>Long Term Bank Facilities BB (120.0 Cr); Short Term Bank Facilitie A4 (85.0 Cr)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Jhaver Group</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Zip Industries Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>U33111TN1956PTC003366</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>AAACZ0949E</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>ZIP INDUSTRIES PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Tamil Nadu, West Bengal</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>ZIP INDUSTRIES LIMITED</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>ZIP INDUSTRIES LIMITED NO.12, G.S.T ROAD,CHENGALPATTU,TAMIL NADU,603001,India</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>Payment After Due Date in last 12 Months.</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>139</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>30.43</v>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>CRISIL</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>Cash Credit B (7.5 Cr); Inland/Import Letter of C A4 (2.5 Cr)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Jhaver Group</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Arqivo (Tagros B2C subsidiary)</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Subsidiary of Tagros (CIN TBC)</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr"/>
+      <c r="F9" s="2" t="inlineStr"/>
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr"/>
+      <c r="O9" s="2" t="inlineStr"/>
+      <c r="P9" s="2" t="inlineStr"/>
+      <c r="Q9" s="2" t="inlineStr"/>
+      <c r="R9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Jhaver Group</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Prodapt Infrastructure / Prologis JV</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>TBC (JV vehicle)</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr"/>
+      <c r="F10" s="2" t="inlineStr"/>
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr"/>
+      <c r="O10" s="2" t="inlineStr"/>
+      <c r="P10" s="2" t="inlineStr"/>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="50" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Endpoint</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Status on supplied key</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Returns</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Use in this file</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>/probe_data_api/entities/{cin}/open-charges</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>✅ 200 OK</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>MCA charge register entries — id, date, holder_name, amount, status (Creation/Modification)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Used in main dossier (Sections 02–07). Counted + summed in Company Master.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>/probe_data_api/entities/{cin}/gst-details</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>✅ 200 OK</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Active GSTINs by state, taxpayer type, return-filing timeliness, business activity</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Used to derive company PAN (chars 3–12 of GSTIN) and state coverage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>/probe_data_api/entities/{cin}/epfo-details</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>✅ 200 OK</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>EPFO establishment id, name, address, exemption status, monthly filings (TRRN, employees, amount, timeliness)</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Avg monthly employee count, address, PF payment timeliness.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>/probe_data_api/entities/{cin}/credit-ratings</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>✅ 200 OK</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Per-agency rating actions (CRISIL/ICRA/CARE) with instrument-level amount, rating, action, outlook</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Latest rating + top instruments listed in Company Master.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>/v1/entities/{cin}/directors</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>❌ 403 Forbidden (route exists, key out of scope)</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Director name, DIN, status, network of companies (designation + dates)</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Would populate Director Name + DIN + Designation columns automatically.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>/v2/entities/{cin}/directors</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>❌ 403 Forbidden (same)</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Same as v1 + extra metadata</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Same use as v1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>/v1/entities/{cin}/identification-and-status</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>❌ 403 Forbidden</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Vitals incl. pan_of_entity, type_of_entity, registered_address, LEI, name history, last AGM, industry segment, key indicators</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Would replace GSTIN-derivation with first-party PAN + add industry classification.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>/v1/directors/{din}/* and /v2/directors/{din}/*</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>❌ 403 Forbidden (route exists)</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Likely director profile by DIN (KYC product — to be confirmed)</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Best candidate for fetching director PAN/DOB if it exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Director PAN</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>❌ NOT in any tested endpoint</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Director PAN is not in any endpoint accessible with this key. Likely a separate Probe42 KYC SKU or comes from internal CIBIL/PODS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Director DoB</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>❌ NOT in any tested endpoint</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Same as above. MCA DIR-3 form has DoB but is not exposed via Probe42 directors endpoint per the schema you shared.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="130" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Source / Status</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>A/c Holder (Director Name)</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="inlineStr">
-        <is>
-          <t>MCA / company website / dossier research</t>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Director Name / Designation / DIN</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Public sources (MCA portal director listing, ZaubaCorp, company press, Prodapt leadership page, Tagros annual report director list, MCA Form DIR-12 filings) where DIN is publicly known.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>Realtime Designation</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>MCA / company press releases / LinkedIn (Apr 2026)</t>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Company PAN (Probe42 GSTIN-derived)</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Computed from active GSTINs returned by /probe_data_api/entities/{cin}/gst-details. The 15-char GSTIN encodes the 10-char PAN at positions 3–12. Cross-verified across multiple states for the same entity to confirm consistency.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>DIN</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>MCA — populated where publicly known; remainder to be filled from licensed Probe42 directors API</t>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Legal Name / GSTIN count / States</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>/probe_data_api/entities/{cin}/gst-details — same call as above.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>PODS PAN</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>Director PAN is not in the public MCA register. Source: internal CIBIL / PODS / Probe42 directors API (requires director-scoped key — the open-charges key supplied does not have this scope)</t>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>EPFO data</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>/probe_data_api/entities/{cin}/epfo-details — establishment id, address, monthly TRRN filings, employee count from latest filings.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>DoI-DoB</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>Date of Birth from MCA DIR-3 — accessible via Probe42 directors API (scope-locked on key supplied)</t>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Open Charges count + total</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>/probe_data_api/entities/{cin}/open-charges — already used in the main dossier (Section 02 onwards).</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>Mobile No / Email ID</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed — internal CRM / Probe42 enrichment</t>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Credit Ratings</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>/probe_data_api/entities/{cin}/credit-ratings — instrument-level CRISIL/ICRA/CARE actions.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr"/>
-      <c r="B8" s="5" t="inlineStr"/>
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>PODS PAN (director-level)</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>NOT populated. Director PAN is not exposed in any Probe42 endpoint reachable on the supplied open-charges-scoped key. The directors endpoint schema shared by the user shows only name, DIN, din_status, and network of companies/LLPs — no PAN or DOB. Director PAN typically requires a Probe42 KYC SKU (DIN-keyed) or internal CIBIL Commercial Bureau / PODS enrichment.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>Probe42 endpoint observation</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>/v1/entities/{cin}/directors and /v2/entities/{cin}/directors return HTTP 403 'Forbidden' on the supplied API key (open-charges scoped). /open-charges returns 200. Request a director-scoped key from Probe42 to auto-populate the empty columns.</t>
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>DoI-DoB (director-level)</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>NOT populated. Same as above — DOB is not exposed in the directors endpoint schema. MCA DIR-3 form contains DOB but is not returned via Probe42's directors API per the schema shared.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr"/>
-      <c r="B10" s="5" t="inlineStr"/>
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Mobile / Email</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>NOT populated. Director contact details are not in any public registry or in the Probe42 directors endpoint schema. Source: internal CRM only.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>CINs marked TBC</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>TIL Healthcare, JU Agri Sciences, Zip Industries, Arqivo, Prodapt Infrastructure — to be confirmed from MCA portal master search.</t>
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Probe42 endpoint matrix</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>See sheet 'Probe42 Endpoint Map' for the full list of endpoints tested, what they return, and which ones the supplied key can hit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Arqivo / Prologis JV CIN</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Not yet identified in MCA public search (Arqivo is a Tagros B2C subsidiary; Prologis-Jhaver JV vehicle CIN not yet in public domain).</t>
         </is>
       </c>
     </row>
